--- a/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
+++ b/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="606">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -2249,7 +2249,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -2258,6 +2258,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="5" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="4.86"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="22" min="14" style="0" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="1" width="9.33"/>
   </cols>
   <sheetData>
@@ -2347,8 +2348,11 @@
       <c r="V2" s="3" t="n">
         <v>45931</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="W2" s="3" t="n">
         <v>45938</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>45792</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2417,8 +2421,11 @@
       <c r="V3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2487,7 +2494,10 @@
       <c r="V4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W4" s="6" t="s">
+      <c r="W4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2557,7 +2567,10 @@
       <c r="V5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W5" s="6" t="s">
+      <c r="W5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X5" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2627,7 +2640,10 @@
       <c r="V6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="W6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X6" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2697,7 +2713,10 @@
       <c r="V7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="W7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X7" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2767,7 +2786,10 @@
       <c r="V8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="W8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2837,7 +2859,10 @@
       <c r="V9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="W9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2907,7 +2932,10 @@
       <c r="V10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W10" s="6" t="s">
+      <c r="W10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2977,7 +3005,10 @@
       <c r="V11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W11" s="6" t="s">
+      <c r="W11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X11" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3047,7 +3078,10 @@
       <c r="V12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W12" s="6" t="s">
+      <c r="W12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X12" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3117,7 +3151,10 @@
       <c r="V13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W13" s="6" t="s">
+      <c r="W13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X13" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3187,7 +3224,10 @@
       <c r="V14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="6" t="s">
+      <c r="W14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3257,7 +3297,10 @@
       <c r="V15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W15" s="6" t="s">
+      <c r="W15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X15" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3327,7 +3370,10 @@
       <c r="V16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W16" s="6" t="s">
+      <c r="W16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X16" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3397,7 +3443,10 @@
       <c r="V17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W17" s="6" t="s">
+      <c r="W17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X17" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3467,7 +3516,10 @@
       <c r="V18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W18" s="6" t="s">
+      <c r="W18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X18" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3537,7 +3589,10 @@
       <c r="V19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W19" s="6" t="s">
+      <c r="W19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X19" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3607,7 +3662,10 @@
       <c r="V20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W20" s="6" t="s">
+      <c r="W20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X20" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3680,7 +3738,10 @@
       <c r="V21" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="W21" s="6" t="s">
+      <c r="W21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X21" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3750,8 +3811,11 @@
       <c r="V22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W22" s="6" t="s">
+      <c r="W22" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="X22" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3820,7 +3884,10 @@
       <c r="V23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W23" s="6" t="s">
+      <c r="W23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X23" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3890,7 +3957,10 @@
       <c r="V24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W24" s="6" t="s">
+      <c r="W24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="X24" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3958,6 +4028,10 @@
       <c r="W25" s="1" t="n">
         <f aca="false">COUNTIF(W3:W24,"P")</f>
         <v>19</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <f aca="false">COUNTIF(X3:X24,"P")</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -5051,7 +5125,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr defaultColWidth="9.6640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
@@ -5590,6 +5664,12 @@
       </c>
       <c r="J23" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G24" s="6" t="n">
+        <f aca="false">MAX(G2:G23)</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7120,7 +7200,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="19" min="3" style="0" width="9.66"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="19" min="3" style="1" width="9.66"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="23.32"/>
   </cols>
   <sheetData>
@@ -7333,7 +7413,7 @@
       <c r="X3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AB3" s="0" t="n">
+      <c r="AB3" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7399,7 +7479,10 @@
       <c r="W4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AB4" s="0" t="n">
+      <c r="X4" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB4" s="1" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7459,7 +7542,10 @@
       <c r="W5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB5" s="0" t="n">
+      <c r="X5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7528,7 +7614,10 @@
       <c r="W6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" s="0" t="n">
+      <c r="X6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7594,7 +7683,10 @@
       <c r="W7" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AB7" s="0" t="n">
+      <c r="X7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7654,7 +7746,10 @@
       <c r="W8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB8" s="0" t="n">
+      <c r="X8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB8" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7714,7 +7809,10 @@
       <c r="W9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB9" s="0" t="n">
+      <c r="X9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7780,7 +7878,10 @@
       <c r="W10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB10" s="0" t="n">
+      <c r="X10" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7843,7 +7944,7 @@
       <c r="W11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB11" s="0" t="n">
+      <c r="AB11" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7906,7 +8007,7 @@
       <c r="W12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB12" s="0" t="n">
+      <c r="AB12" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7966,7 +8067,7 @@
       <c r="W13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AB13" s="0" t="n">
+      <c r="AB13" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8038,7 +8139,7 @@
       <c r="W14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB14" s="0" t="n">
+      <c r="AB14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8101,7 +8202,7 @@
       <c r="W15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB15" s="0" t="n">
+      <c r="AB15" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8164,7 +8265,7 @@
       <c r="W16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AB16" s="0" t="n">
+      <c r="AB16" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8224,7 +8325,7 @@
       <c r="W17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB17" s="0" t="n">
+      <c r="AB17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8293,7 +8394,7 @@
       <c r="W18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB18" s="0" t="n">
+      <c r="AB18" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8363,7 +8464,7 @@
       <c r="W19" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB19" s="0" t="n">
+      <c r="AB19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8429,6 +8530,9 @@
       <c r="W20" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AB20" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -8561,7 +8665,7 @@
       <c r="W22" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB22" s="0" t="n">
+      <c r="AB22" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8624,7 +8728,7 @@
       <c r="W23" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AB23" s="0" t="n">
+      <c r="AB23" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8633,10 +8737,10 @@
         <f aca="false">COUNTIF(U2:U23,"P")</f>
         <v>18</v>
       </c>
-      <c r="AA24" s="6" t="s">
+      <c r="AA24" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AB24" s="6" t="n">
+      <c r="AB24" s="2" t="n">
         <f aca="false">COUNTIF(AB2:AB23,"&gt;0")</f>
         <v>19</v>
       </c>

--- a/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
+++ b/inasistencias-5a-Electornica/alumnos-5a-Electronica.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="650">
   <si>
     <t xml:space="preserve">total </t>
   </si>
@@ -2023,7 +2023,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2046,6 +2046,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFBF00"/>
         <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
   </fills>
@@ -2090,7 +2102,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2112,10 +2124,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2147,10 +2155,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2159,23 +2163,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2315,14 +2315,14 @@
       <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF4000"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -2454,8 +2454,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="5" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="4.86"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="14" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="29" style="0" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="14" style="1" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="1" width="9.33"/>
   </cols>
   <sheetData>
@@ -2588,7 +2587,7 @@
       <c r="AG2" s="5" t="n">
         <v>45994</v>
       </c>
-      <c r="AH2" s="6" t="n">
+      <c r="AH2" s="3" t="n">
         <v>46001</v>
       </c>
       <c r="AI2" s="2"/>
@@ -2635,7 +2634,7 @@
         <f aca="false">COUNTIF(E3:L3,"P")</f>
         <v>8</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="O3" s="6" t="n">
         <f aca="false">ROUND(N3*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -2675,7 +2674,7 @@
       <c r="AA3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="8" t="s">
+      <c r="AB3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC3" s="2" t="n">
@@ -2690,7 +2689,7 @@
         <f aca="false">COUNTIF(P3:AA3,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="9" t="n">
+      <c r="AF3" s="8" t="n">
         <f aca="false">ROUND((AC3+AD3/2*AE3/4)*10/12,0)</f>
         <v>9</v>
       </c>
@@ -2736,7 +2735,7 @@
         <f aca="false">COUNTIF(E4:L4,"P")</f>
         <v>8</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="6" t="n">
         <f aca="false">ROUND(N4*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -2776,7 +2775,7 @@
       <c r="AA4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB4" s="8" t="s">
+      <c r="AB4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC4" s="2" t="n">
@@ -2791,7 +2790,7 @@
         <f aca="false">COUNTIF(P4:AA4,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF4" s="9" t="n">
+      <c r="AF4" s="8" t="n">
         <f aca="false">ROUND((AC4+AD4/2*AE4/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -2837,7 +2836,7 @@
         <f aca="false">COUNTIF(E5:L5,"P")</f>
         <v>7</v>
       </c>
-      <c r="O5" s="7" t="n">
+      <c r="O5" s="6" t="n">
         <f aca="false">ROUND(N5*10/$P$1,0)</f>
         <v>9</v>
       </c>
@@ -2877,7 +2876,7 @@
       <c r="AA5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB5" s="8" t="s">
+      <c r="AB5" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC5" s="2" t="n">
@@ -2892,7 +2891,7 @@
         <f aca="false">COUNTIF(P5:AA5,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF5" s="9" t="n">
+      <c r="AF5" s="8" t="n">
         <f aca="false">ROUND((AC5+AD5/2*AE5/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -2938,7 +2937,7 @@
         <f aca="false">COUNTIF(E6:L6,"P")</f>
         <v>8</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="O6" s="6" t="n">
         <f aca="false">ROUND(N6*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -2978,7 +2977,7 @@
       <c r="AA6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB6" s="8" t="s">
+      <c r="AB6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC6" s="2" t="n">
@@ -2993,7 +2992,7 @@
         <f aca="false">COUNTIF(P6:AA6,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF6" s="9" t="n">
+      <c r="AF6" s="8" t="n">
         <f aca="false">ROUND((AC6+AD6/2*AE6/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -3039,7 +3038,7 @@
         <f aca="false">COUNTIF(E7:L7,"P")</f>
         <v>7</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="O7" s="6" t="n">
         <f aca="false">ROUND(N7*10/$P$1,0)</f>
         <v>9</v>
       </c>
@@ -3079,7 +3078,7 @@
       <c r="AA7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB7" s="8" t="s">
+      <c r="AB7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC7" s="2" t="n">
@@ -3094,7 +3093,7 @@
         <f aca="false">COUNTIF(P7:AA7,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="9" t="n">
+      <c r="AF7" s="8" t="n">
         <f aca="false">ROUND((AC7+AD7/2*AE7/4)*10/12,0)</f>
         <v>8</v>
       </c>
@@ -3140,7 +3139,7 @@
         <f aca="false">COUNTIF(E8:L8,"P")</f>
         <v>8</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="6" t="n">
         <f aca="false">ROUND(N8*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -3180,7 +3179,7 @@
       <c r="AA8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB8" s="8" t="s">
+      <c r="AB8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC8" s="2" t="n">
@@ -3195,7 +3194,7 @@
         <f aca="false">COUNTIF(P8:AA8,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="9" t="n">
+      <c r="AF8" s="8" t="n">
         <f aca="false">ROUND((AC8+AD8/2*AE8/4)*10/12,0)</f>
         <v>9</v>
       </c>
@@ -3241,7 +3240,7 @@
         <f aca="false">COUNTIF(E9:L9,"P")</f>
         <v>8</v>
       </c>
-      <c r="O9" s="7" t="n">
+      <c r="O9" s="6" t="n">
         <f aca="false">ROUND(N9*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -3281,7 +3280,7 @@
       <c r="AA9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB9" s="8" t="s">
+      <c r="AB9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC9" s="2" t="n">
@@ -3296,7 +3295,7 @@
         <f aca="false">COUNTIF(P9:AA9,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF9" s="9" t="n">
+      <c r="AF9" s="8" t="n">
         <f aca="false">ROUND((AC9+AD9/2*AE9/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -3342,7 +3341,7 @@
         <f aca="false">COUNTIF(E10:L10,"P")</f>
         <v>8</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="O10" s="6" t="n">
         <f aca="false">ROUND(N10*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -3382,7 +3381,7 @@
       <c r="AA10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB10" s="8" t="s">
+      <c r="AB10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC10" s="2" t="n">
@@ -3397,7 +3396,7 @@
         <f aca="false">COUNTIF(P10:AA10,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="9" t="n">
+      <c r="AF10" s="8" t="n">
         <f aca="false">ROUND((AC10+AD10/2*AE10/4)*10/12,0)</f>
         <v>9</v>
       </c>
@@ -3443,7 +3442,7 @@
         <f aca="false">COUNTIF(E11:L11,"P")</f>
         <v>7</v>
       </c>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="6" t="n">
         <f aca="false">ROUND(N11*10/$P$1,0)</f>
         <v>9</v>
       </c>
@@ -3483,7 +3482,7 @@
       <c r="AA11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB11" s="8" t="s">
+      <c r="AB11" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC11" s="2" t="n">
@@ -3498,7 +3497,7 @@
         <f aca="false">COUNTIF(P11:AA11,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="9" t="n">
+      <c r="AF11" s="8" t="n">
         <f aca="false">ROUND((AC11+AD11/2*AE11/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -3544,7 +3543,7 @@
         <f aca="false">COUNTIF(E12:L12,"P")</f>
         <v>8</v>
       </c>
-      <c r="O12" s="7" t="n">
+      <c r="O12" s="6" t="n">
         <f aca="false">ROUND(N12*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -3584,7 +3583,7 @@
       <c r="AA12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB12" s="8" t="s">
+      <c r="AB12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC12" s="2" t="n">
@@ -3599,7 +3598,7 @@
         <f aca="false">COUNTIF(P12:AA12,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="9" t="n">
+      <c r="AF12" s="8" t="n">
         <f aca="false">ROUND((AC12+AD12/2*AE12/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -3645,7 +3644,7 @@
         <f aca="false">COUNTIF(E13:L13,"P")</f>
         <v>8</v>
       </c>
-      <c r="O13" s="7" t="n">
+      <c r="O13" s="6" t="n">
         <f aca="false">ROUND(N13*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -3685,7 +3684,7 @@
       <c r="AA13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB13" s="8" t="s">
+      <c r="AB13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC13" s="2" t="n">
@@ -3700,7 +3699,7 @@
         <f aca="false">COUNTIF(P13:AA13,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="9" t="n">
+      <c r="AF13" s="8" t="n">
         <f aca="false">ROUND((AC13+AD13/2*AE13/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -3746,7 +3745,7 @@
         <f aca="false">COUNTIF(E14:L14,"P")</f>
         <v>8</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="6" t="n">
         <f aca="false">ROUND(N14*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -3786,7 +3785,7 @@
       <c r="AA14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB14" s="8" t="s">
+      <c r="AB14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC14" s="2" t="n">
@@ -3801,119 +3800,119 @@
         <f aca="false">COUNTIF(P14:AA14,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="9" t="n">
+      <c r="AF14" s="8" t="n">
         <f aca="false">ROUND((AC14+AD14/2*AE14/4)*10/12,0)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="15" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="n">
+    <row r="15" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10" t="n">
+      <c r="E15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9" t="n">
         <f aca="false">COUNTIF(E15:L15,"P")</f>
         <v>8</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="10" t="n">
         <f aca="false">ROUND(N15*10/$P$1,0)</f>
         <v>10</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="10" t="s">
+      <c r="P15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="U15" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V15" s="10" t="s">
+      <c r="R15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="U15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="V15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="W15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="X15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC15" s="8" t="n">
+      <c r="W15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC15" s="7" t="n">
         <f aca="false">COUNTIF(P15:AA15,"P")</f>
         <v>10</v>
       </c>
-      <c r="AD15" s="8" t="n">
+      <c r="AD15" s="7" t="n">
         <f aca="false">COUNTIF(P15:AA15,"M")</f>
         <v>0</v>
       </c>
-      <c r="AE15" s="8" t="n">
+      <c r="AE15" s="7" t="n">
         <f aca="false">COUNTIF(P15:AA15,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="12" t="n">
+      <c r="AF15" s="11" t="n">
         <f aca="false">ROUND((AC15+AD15/2*AE15/4)*10/12,0)</f>
         <v>8</v>
       </c>
-      <c r="AG15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH15" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AMJ15" s="10"/>
+      <c r="AG15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AMJ15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -3956,7 +3955,7 @@
         <f aca="false">COUNTIF(E16:L16,"P")</f>
         <v>8</v>
       </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="6" t="n">
         <f aca="false">ROUND(N16*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -3996,7 +3995,7 @@
       <c r="AA16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB16" s="8" t="s">
+      <c r="AB16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC16" s="2" t="n">
@@ -4011,7 +4010,7 @@
         <f aca="false">COUNTIF(P16:AA16,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="9" t="n">
+      <c r="AF16" s="8" t="n">
         <f aca="false">ROUND((AC16+AD16/2*AE16/4)*10/12,0)</f>
         <v>9</v>
       </c>
@@ -4057,7 +4056,7 @@
         <f aca="false">COUNTIF(E17:L17,"P")</f>
         <v>8</v>
       </c>
-      <c r="O17" s="7" t="n">
+      <c r="O17" s="6" t="n">
         <f aca="false">ROUND(N17*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -4097,7 +4096,7 @@
       <c r="AA17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB17" s="8" t="s">
+      <c r="AB17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC17" s="2" t="n">
@@ -4112,228 +4111,228 @@
         <f aca="false">COUNTIF(P17:AA17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF17" s="9" t="n">
+      <c r="AF17" s="8" t="n">
         <f aca="false">ROUND((AC17+AD17/2*AE17/4)*10/12,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="18" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n">
+    <row r="18" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="10" t="s">
+      <c r="E18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10" t="n">
+      <c r="G18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9" t="n">
         <f aca="false">COUNTIF(E18:L18,"P")</f>
         <v>7</v>
       </c>
-      <c r="O18" s="11" t="n">
+      <c r="O18" s="10" t="n">
         <f aca="false">ROUND(N18*10/$P$1,0)</f>
         <v>9</v>
       </c>
-      <c r="P18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="R18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S18" s="10" t="s">
+      <c r="P18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="S18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="T18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="U18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V18" s="10" t="s">
+      <c r="T18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="U18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="V18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="W18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="X18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y18" s="8" t="s">
+      <c r="W18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="Z18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB18" s="8" t="s">
+      <c r="Z18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AC18" s="8" t="n">
+      <c r="AC18" s="7" t="n">
         <f aca="false">COUNTIF(P18:AA18,"P")</f>
         <v>9</v>
       </c>
-      <c r="AD18" s="8" t="n">
+      <c r="AD18" s="7" t="n">
         <f aca="false">COUNTIF(P18:AA18,"M")</f>
         <v>0</v>
       </c>
-      <c r="AE18" s="8" t="n">
+      <c r="AE18" s="7" t="n">
         <f aca="false">COUNTIF(P18:AA18,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF18" s="12" t="n">
+      <c r="AF18" s="11" t="n">
         <f aca="false">ROUND((AC18+AD18/2*AE18/4)*10/12,0)</f>
         <v>8</v>
       </c>
-      <c r="AG18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH18" s="8" t="s">
+      <c r="AG18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AMJ18" s="10"/>
-    </row>
-    <row r="19" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n">
+      <c r="AMJ18" s="9"/>
+    </row>
+    <row r="19" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10" t="n">
+      <c r="E19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9" t="n">
         <f aca="false">COUNTIF(E19:L19,"P")</f>
         <v>8</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="10" t="n">
         <f aca="false">ROUND(N19*10/$P$1,0)</f>
         <v>10</v>
       </c>
-      <c r="P19" s="10" t="s">
+      <c r="P19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="10" t="s">
+      <c r="Q19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="U19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V19" s="10" t="s">
+      <c r="R19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="U19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="V19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="W19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="X19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB19" s="8" t="s">
+      <c r="W19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AC19" s="8" t="n">
+      <c r="AC19" s="7" t="n">
         <f aca="false">COUNTIF(P19:AA19,"P")</f>
         <v>9</v>
       </c>
-      <c r="AD19" s="8" t="n">
+      <c r="AD19" s="7" t="n">
         <f aca="false">COUNTIF(P19:AA19,"M")</f>
         <v>0</v>
       </c>
-      <c r="AE19" s="8" t="n">
+      <c r="AE19" s="7" t="n">
         <f aca="false">COUNTIF(P19:AA19,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="12" t="n">
+      <c r="AF19" s="11" t="n">
         <f aca="false">ROUND((AC19+AD19/2*AE19/4)*10/12,0)</f>
         <v>8</v>
       </c>
-      <c r="AG19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH19" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AMJ19" s="10"/>
+      <c r="AG19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AMJ19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -4376,7 +4375,7 @@
         <f aca="false">COUNTIF(E20:L20,"P")</f>
         <v>8</v>
       </c>
-      <c r="O20" s="7" t="n">
+      <c r="O20" s="6" t="n">
         <f aca="false">ROUND(N20*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -4416,7 +4415,7 @@
       <c r="AA20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB20" s="8" t="s">
+      <c r="AB20" s="7" t="s">
         <v>16</v>
       </c>
       <c r="AC20" s="2" t="n">
@@ -4431,7 +4430,7 @@
         <f aca="false">COUNTIF(P20:AA20,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="9" t="n">
+      <c r="AF20" s="8" t="n">
         <f aca="false">ROUND((AC20+AD20/2*AE20/4)*10/12,0)</f>
         <v>10</v>
       </c>
@@ -4480,7 +4479,7 @@
         <f aca="false">COUNTIF(E21:L21,"P")</f>
         <v>7</v>
       </c>
-      <c r="O21" s="7" t="n">
+      <c r="O21" s="6" t="n">
         <f aca="false">ROUND(N21*10/$P$1,0)</f>
         <v>9</v>
       </c>
@@ -4520,7 +4519,7 @@
       <c r="AA21" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AB21" s="8" t="s">
+      <c r="AB21" s="7" t="s">
         <v>72</v>
       </c>
       <c r="AC21" s="2" t="n">
@@ -4535,7 +4534,7 @@
         <f aca="false">COUNTIF(P21:AA21,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF21" s="9" t="n">
+      <c r="AF21" s="8" t="n">
         <f aca="false">ROUND((AC21+AD21/2*AE21/4)*10/12,0)</f>
         <v>0</v>
       </c>
@@ -4581,7 +4580,7 @@
         <f aca="false">COUNTIF(E22:L22,"P")</f>
         <v>8</v>
       </c>
-      <c r="O22" s="7" t="n">
+      <c r="O22" s="6" t="n">
         <f aca="false">ROUND(N22*10/$P$1,0)</f>
         <v>10</v>
       </c>
@@ -4621,7 +4620,7 @@
       <c r="AA22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB22" s="8" t="s">
+      <c r="AB22" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC22" s="2" t="n">
@@ -4636,7 +4635,7 @@
         <f aca="false">COUNTIF(P22:AA22,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF22" s="9" t="n">
+      <c r="AF22" s="8" t="n">
         <f aca="false">ROUND((AC22+AD22/2*AE22/4)*10/12,0)</f>
         <v>9</v>
       </c>
@@ -4682,7 +4681,7 @@
         <f aca="false">COUNTIF(E23:L23,"P")</f>
         <v>7</v>
       </c>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="6" t="n">
         <f aca="false">ROUND(N23*10/$P$1,0)</f>
         <v>9</v>
       </c>
@@ -4722,7 +4721,7 @@
       <c r="AA23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AB23" s="8" t="s">
+      <c r="AB23" s="7" t="s">
         <v>15</v>
       </c>
       <c r="AC23" s="2" t="n">
@@ -4737,119 +4736,119 @@
         <f aca="false">COUNTIF(P23:AA23,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF23" s="9" t="n">
+      <c r="AF23" s="8" t="n">
         <f aca="false">ROUND((AC23+AD23/2*AE23/4)*10/12,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="24" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="n">
+    <row r="24" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10" t="n">
+      <c r="E24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9" t="n">
         <f aca="false">COUNTIF(E24:L24,"P")</f>
         <v>8</v>
       </c>
-      <c r="O24" s="11" t="n">
+      <c r="O24" s="10" t="n">
         <f aca="false">ROUND(N24*10/$P$1,0)</f>
         <v>10</v>
       </c>
-      <c r="P24" s="10" t="s">
+      <c r="P24" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Q24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="R24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="T24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="U24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="V24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="W24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="X24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y24" s="8" t="s">
+      <c r="Q24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="U24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="V24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="W24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y24" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="Z24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC24" s="8" t="n">
+      <c r="Z24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC24" s="7" t="n">
         <f aca="false">COUNTIF(P24:AA24,"P")</f>
         <v>10</v>
       </c>
-      <c r="AD24" s="8" t="n">
+      <c r="AD24" s="7" t="n">
         <f aca="false">COUNTIF(P24:AA24,"M")</f>
         <v>0</v>
       </c>
-      <c r="AE24" s="8" t="n">
+      <c r="AE24" s="7" t="n">
         <f aca="false">COUNTIF(P24:AA24,"T")</f>
         <v>0</v>
       </c>
-      <c r="AF24" s="12" t="n">
+      <c r="AF24" s="11" t="n">
         <f aca="false">ROUND((AC24+AD24/2*AE24/4)*10/12,0)</f>
         <v>8</v>
       </c>
-      <c r="AG24" s="8" t="s">
+      <c r="AG24" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AH24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AMJ24" s="10"/>
+      <c r="AH24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AMJ24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="1" t="n">
@@ -5429,7 +5428,7 @@
       <c r="F17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I17" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6455,7 +6454,7 @@
       <c r="F9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="9" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9991,20 +9990,18 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="19" min="3" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="23.32"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="24" min="21" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="25" min="25" style="1" width="10.88"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="26" min="26" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="27" min="27" style="1" width="18.76"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="30" min="28" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="31" style="0" width="9.66"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="32" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="33" min="33" style="1" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="34" style="1" width="19.69"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="35" style="0" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="36" min="36" style="1" width="56.68"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="39" min="37" style="0" width="9.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="3" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="23.32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="24" min="21" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="10.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="18.76"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="32" min="28" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="13.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="19.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="56.68"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="39" min="37" style="1" width="9.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10044,13 +10041,13 @@
       <c r="AL1" s="3" t="n">
         <v>45945</v>
       </c>
-      <c r="AM1" s="14" t="s">
+      <c r="AM1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AP1" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ1" s="0" t="n">
+      <c r="AP1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ1" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10158,16 +10155,16 @@
       <c r="AL2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AM2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AN2" s="14" t="s">
+      <c r="AN2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AP2" s="14" t="s">
+      <c r="AP2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AQ2" s="14" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
@@ -10181,19 +10178,19 @@
       <c r="C3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="9" t="n">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="I3" s="9" t="n">
         <v>7</v>
       </c>
       <c r="J3" s="3" t="n">
@@ -10206,11 +10203,11 @@
         <f aca="false">I3+K3/2</f>
         <v>8.5</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C3,E3,G3,L3),0)</f>
         <v>6</v>
       </c>
-      <c r="N3" s="9" t="str">
+      <c r="N3" s="8" t="str">
         <f aca="false">IF(M3&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
@@ -10223,7 +10220,7 @@
       <c r="R3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S3" s="9" t="n">
+      <c r="S3" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O3:R3,M3),0)</f>
         <v>8</v>
       </c>
@@ -10233,10 +10230,10 @@
       <c r="V3" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="X3" s="15" t="n">
+      <c r="X3" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="Y3" s="15" t="s">
+      <c r="Y3" s="13" t="s">
         <v>112</v>
       </c>
       <c r="Z3" s="1" t="n">
@@ -10255,16 +10252,14 @@
         <f aca="false">AB3+AC3/2</f>
         <v>10.5</v>
       </c>
-      <c r="AE3" s="9" t="n">
+      <c r="AE3" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z3,X3,V3,AD3),0)</f>
         <v>8</v>
       </c>
-      <c r="AF3" s="9" t="n">
+      <c r="AF3" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S3,AE3),0)</f>
         <v>8</v>
       </c>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="9"/>
       <c r="AI3" s="1" t="n">
         <v>4</v>
       </c>
@@ -10298,11 +10293,11 @@
         <f aca="false">I4+K4/2</f>
         <v>9</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C4,E4,G4,L4),0)</f>
         <v>8</v>
       </c>
-      <c r="N4" s="9" t="str">
+      <c r="N4" s="8" t="str">
         <f aca="false">IF(M4&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10315,7 +10310,7 @@
       <c r="R4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O4:R4,M4),0)</f>
         <v>8</v>
       </c>
@@ -10341,16 +10336,14 @@
         <f aca="false">AB4+AC4/2</f>
         <v>10</v>
       </c>
-      <c r="AE4" s="9" t="n">
+      <c r="AE4" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z4,X4,V4,AD4),0)</f>
         <v>10</v>
       </c>
-      <c r="AF4" s="9" t="n">
+      <c r="AF4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S4,AE4),0)</f>
         <v>9</v>
       </c>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
       <c r="AI4" s="1" t="n">
         <v>4</v>
       </c>
@@ -10371,13 +10364,13 @@
       <c r="E5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="9" t="n">
         <v>7.5</v>
       </c>
       <c r="J5" s="3" t="n">
@@ -10390,11 +10383,11 @@
         <f aca="false">I5+K5/2</f>
         <v>8.5</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C5,E5,G5,L5),0)</f>
         <v>8</v>
       </c>
-      <c r="N5" s="9" t="str">
+      <c r="N5" s="8" t="str">
         <f aca="false">IF(M5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10407,7 +10400,7 @@
       <c r="R5" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O5:R5,M5),0)</f>
         <v>8</v>
       </c>
@@ -10433,16 +10426,14 @@
         <f aca="false">AB5+AC5/2</f>
         <v>12</v>
       </c>
-      <c r="AE5" s="9" t="n">
+      <c r="AE5" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z5,X5,V5,AD5),0)</f>
         <v>9</v>
       </c>
-      <c r="AF5" s="9" t="n">
+      <c r="AF5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S5,AE5),0)</f>
         <v>9</v>
       </c>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
       <c r="AI5" s="1" t="n">
         <v>4</v>
       </c>
@@ -10476,11 +10467,11 @@
         <f aca="false">I6+K6/2</f>
         <v>11</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C6,E6,G6,L6),0)</f>
         <v>10</v>
       </c>
-      <c r="N6" s="9" t="str">
+      <c r="N6" s="8" t="str">
         <f aca="false">IF(M6&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10493,7 +10484,7 @@
       <c r="R6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O6:R6,M6),0)</f>
         <v>10</v>
       </c>
@@ -10519,20 +10510,18 @@
         <f aca="false">AB6+AC6/2</f>
         <v>12</v>
       </c>
-      <c r="AE6" s="9" t="n">
+      <c r="AE6" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z6,X6,V6,AD6),0)</f>
         <v>10</v>
       </c>
-      <c r="AF6" s="9" t="n">
+      <c r="AF6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S6,AE6),0)</f>
         <v>10</v>
       </c>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
       <c r="AI6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AJ6" s="16" t="s">
+      <c r="AJ6" s="14" t="s">
         <v>116</v>
       </c>
     </row>
@@ -10568,11 +10557,11 @@
         <f aca="false">I7+K7/2</f>
         <v>8.5</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C7,E7,G7,L7),0)</f>
         <v>8</v>
       </c>
-      <c r="N7" s="9" t="str">
+      <c r="N7" s="8" t="str">
         <f aca="false">IF(M7&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10588,7 +10577,7 @@
       <c r="R7" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O7:R7,M7),0)</f>
         <v>7</v>
       </c>
@@ -10626,24 +10615,20 @@
         <f aca="false">AB7+AC7/2</f>
         <v>8</v>
       </c>
-      <c r="AE7" s="9" t="n">
+      <c r="AE7" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z7,X7,V7,AD7),0)</f>
         <v>7</v>
       </c>
-      <c r="AF7" s="9" t="n">
+      <c r="AF7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S7,AE7),0)</f>
         <v>7</v>
       </c>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
       <c r="AI7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AJ7" s="16" t="s">
+      <c r="AJ7" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="XFC7" s="0"/>
-      <c r="XFD7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -10658,13 +10643,13 @@
       <c r="E8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="9" t="n">
         <v>8</v>
       </c>
       <c r="J8" s="3" t="n">
@@ -10677,11 +10662,11 @@
         <f aca="false">I8+K8/2</f>
         <v>8</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,L8),0)</f>
         <v>8</v>
       </c>
-      <c r="N8" s="9" t="str">
+      <c r="N8" s="8" t="str">
         <f aca="false">IF(M8&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10694,7 +10679,7 @@
       <c r="R8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O8:R8,M8),0)</f>
         <v>9</v>
       </c>
@@ -10707,36 +10692,34 @@
       <c r="X8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Z8" s="10" t="n">
+      <c r="Z8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AA8" s="8" t="s">
+      <c r="AA8" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="AB8" s="8" t="n">
+      <c r="AB8" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AC8" s="8" t="n">
+      <c r="AC8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="AD8" s="1" t="n">
         <f aca="false">AB8+AC8/2</f>
         <v>10</v>
       </c>
-      <c r="AE8" s="9" t="n">
+      <c r="AE8" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z8,X8,V8,AD8),0)</f>
         <v>9</v>
       </c>
-      <c r="AF8" s="9" t="n">
+      <c r="AF8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S8,AE8),0)</f>
         <v>9</v>
       </c>
-      <c r="AG8" s="9"/>
-      <c r="AH8" s="9"/>
       <c r="AI8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AJ8" s="16" t="s">
+      <c r="AJ8" s="14" t="s">
         <v>123</v>
       </c>
     </row>
@@ -10766,11 +10749,11 @@
         <f aca="false">I9+K9/2</f>
         <v>4.5</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C9,E9,G9,L9),0)</f>
         <v>7</v>
       </c>
-      <c r="N9" s="9" t="str">
+      <c r="N9" s="8" t="str">
         <f aca="false">IF(M9&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10783,7 +10766,7 @@
       <c r="R9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S9" s="9" t="n">
+      <c r="S9" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O9:R9,M9),0)</f>
         <v>9</v>
       </c>
@@ -10809,16 +10792,14 @@
         <f aca="false">AB9+AC9/2</f>
         <v>14</v>
       </c>
-      <c r="AE9" s="9" t="n">
+      <c r="AE9" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z9,X9,V9,AD9),0)</f>
         <v>9</v>
       </c>
-      <c r="AF9" s="9" t="n">
+      <c r="AF9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S9,AE9),0)</f>
         <v>9</v>
       </c>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="9"/>
       <c r="AI9" s="1" t="n">
         <v>4</v>
       </c>
@@ -10852,11 +10833,11 @@
         <f aca="false">I10+K10/2</f>
         <v>9.5</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C10,E10,G10,L10),0)</f>
         <v>10</v>
       </c>
-      <c r="N10" s="9" t="str">
+      <c r="N10" s="8" t="str">
         <f aca="false">IF(M10&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10869,7 +10850,7 @@
       <c r="R10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O10:R10,M10),0)</f>
         <v>10</v>
       </c>
@@ -10895,20 +10876,18 @@
         <f aca="false">AB10+AC10/2</f>
         <v>11.5</v>
       </c>
-      <c r="AE10" s="9" t="n">
+      <c r="AE10" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z10,X10,V10,AD10),0)</f>
         <v>10</v>
       </c>
-      <c r="AF10" s="9" t="n">
+      <c r="AF10" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S10,AE10),0)</f>
         <v>10</v>
       </c>
-      <c r="AG10" s="9"/>
-      <c r="AH10" s="9"/>
       <c r="AI10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AJ10" s="16" t="s">
+      <c r="AJ10" s="14" t="s">
         <v>124</v>
       </c>
     </row>
@@ -10925,13 +10904,13 @@
       <c r="E11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="9" t="n">
         <v>8</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I11" s="9" t="n">
         <v>6</v>
       </c>
       <c r="J11" s="3" t="n">
@@ -10944,11 +10923,11 @@
         <f aca="false">I11+K11/2</f>
         <v>8</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,L11),0)</f>
         <v>8</v>
       </c>
-      <c r="N11" s="9" t="str">
+      <c r="N11" s="8" t="str">
         <f aca="false">IF(M11&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -10961,7 +10940,7 @@
       <c r="R11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O11:R11,M11),0)</f>
         <v>8</v>
       </c>
@@ -10971,10 +10950,10 @@
       <c r="V11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="X11" s="15" t="n">
+      <c r="X11" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="Y11" s="15" t="s">
+      <c r="Y11" s="13" t="s">
         <v>112</v>
       </c>
       <c r="Z11" s="1" t="n">
@@ -10990,16 +10969,14 @@
         <f aca="false">AB11+AC11/2</f>
         <v>12.5</v>
       </c>
-      <c r="AE11" s="9" t="n">
+      <c r="AE11" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z11,X11,V11,AD11),0)</f>
         <v>8</v>
       </c>
-      <c r="AF11" s="9" t="n">
+      <c r="AF11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S11,AE11),0)</f>
         <v>8</v>
       </c>
-      <c r="AG11" s="9"/>
-      <c r="AH11" s="9"/>
       <c r="AI11" s="1" t="n">
         <v>6</v>
       </c>
@@ -11039,11 +11016,11 @@
         <f aca="false">I12+K12/2</f>
         <v>10</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,G12,L12),0)</f>
         <v>8</v>
       </c>
-      <c r="N12" s="9" t="str">
+      <c r="N12" s="8" t="str">
         <f aca="false">IF(M12&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -11057,7 +11034,7 @@
       <c r="R12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="S12" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O12:R12,M12),0)</f>
         <v>7</v>
       </c>
@@ -11089,24 +11066,20 @@
         <f aca="false">AB12+AC12/2</f>
         <v>11.5</v>
       </c>
-      <c r="AE12" s="9" t="n">
+      <c r="AE12" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z12,X12,V12,AD12),0)</f>
         <v>7</v>
       </c>
-      <c r="AF12" s="9" t="n">
+      <c r="AF12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA12,Y12,W12,AE12),0)</f>
         <v>7</v>
       </c>
-      <c r="AG12" s="9"/>
-      <c r="AH12" s="9"/>
       <c r="AI12" s="2" t="n">
         <v>6</v>
       </c>
       <c r="AJ12" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="XFC12" s="0"/>
-      <c r="XFD12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -11124,7 +11097,7 @@
       <c r="G13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I13" s="9" t="n">
         <v>6</v>
       </c>
       <c r="J13" s="3" t="n">
@@ -11137,11 +11110,11 @@
         <f aca="false">I13+K13/2</f>
         <v>9.5</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C13,E13,G13,L13),0)</f>
         <v>8</v>
       </c>
-      <c r="N13" s="9" t="str">
+      <c r="N13" s="8" t="str">
         <f aca="false">IF(M13&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -11154,7 +11127,7 @@
       <c r="R13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O13:R13,M13),0)</f>
         <v>9</v>
       </c>
@@ -11183,20 +11156,18 @@
         <f aca="false">AB13+AC13/2</f>
         <v>12</v>
       </c>
-      <c r="AE13" s="9" t="n">
+      <c r="AE13" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z13,X13,V13,AD13),0)</f>
         <v>9</v>
       </c>
-      <c r="AF13" s="9" t="n">
+      <c r="AF13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S13,AE13),0)</f>
         <v>9</v>
       </c>
-      <c r="AG13" s="9"/>
-      <c r="AH13" s="9"/>
       <c r="AI13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AJ13" s="16" t="s">
+      <c r="AJ13" s="14" t="s">
         <v>124</v>
       </c>
     </row>
@@ -11226,11 +11197,11 @@
         <f aca="false">I14+K14/2</f>
         <v>11.5</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C14,E14,G14,L14),0)</f>
         <v>9</v>
       </c>
-      <c r="N14" s="9" t="str">
+      <c r="N14" s="8" t="str">
         <f aca="false">IF(M14&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -11243,7 +11214,7 @@
       <c r="R14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O14:R14,M14),0)</f>
         <v>9</v>
       </c>
@@ -11272,1076 +11243,1015 @@
         <f aca="false">AB14+AC14/2</f>
         <v>11</v>
       </c>
-      <c r="AE14" s="9" t="n">
+      <c r="AE14" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z14,X14,V14,AD14),0)</f>
         <v>9</v>
       </c>
-      <c r="AF14" s="9" t="n">
+      <c r="AF14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S14,AE14),0)</f>
         <v>9</v>
       </c>
-      <c r="AG14" s="9"/>
-      <c r="AH14" s="9"/>
       <c r="AI14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AJ14" s="16" t="s">
+      <c r="AJ14" s="14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" s="18" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="n">
+    <row r="15" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17" t="n">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="3" t="n">
         <v>45875</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="3" t="n">
         <v>45875</v>
       </c>
-      <c r="K15" s="17" t="n">
+      <c r="K15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="1" t="n">
         <f aca="false">I15+K15/2</f>
         <v>8.5</v>
       </c>
-      <c r="M15" s="20" t="n">
+      <c r="M15" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,L15),0)</f>
         <v>5</v>
       </c>
-      <c r="N15" s="20" t="str">
+      <c r="N15" s="8" t="str">
         <f aca="false">IF(M15&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O15" s="17" t="n">
+      <c r="O15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="P15" s="17" t="s">
+      <c r="P15" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="17" t="n">
+      <c r="Q15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="R15" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S15" s="20" t="n">
+      <c r="R15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O15:R15,M15),0)</f>
         <v>7</v>
       </c>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V15" s="17" t="n">
+      <c r="T15" s="1"/>
+      <c r="U15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y15" s="19" t="n">
+      <c r="W15" s="1"/>
+      <c r="X15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3" t="n">
         <v>45994</v>
       </c>
-      <c r="Z15" s="17" t="n">
+      <c r="Z15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC15" s="17" t="n">
+      <c r="AA15" s="1"/>
+      <c r="AB15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" s="17" t="n">
+      <c r="AD15" s="1" t="n">
         <f aca="false">AB15+AC15/2</f>
         <v>8</v>
       </c>
-      <c r="AE15" s="20" t="n">
+      <c r="AE15" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z15,X15,V15,AD15),0)</f>
         <v>7</v>
       </c>
-      <c r="AF15" s="20" t="n">
+      <c r="AF15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S15,AE15),0)</f>
         <v>7</v>
       </c>
-      <c r="AG15" s="20"/>
-      <c r="AH15" s="20"/>
-      <c r="AI15" s="17" t="n">
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AJ15" s="17"/>
-      <c r="AK15" s="17" t="n">
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AL15" s="17" t="n">
+      <c r="AL15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN15" s="18" t="n">
+      <c r="AN15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AO15" s="18" t="s">
+      <c r="AO15" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="XFC15" s="21"/>
-      <c r="XFD15" s="21"/>
-    </row>
-    <row r="16" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="n">
+      <c r="XFC15" s="1"/>
+      <c r="XFD15" s="1"/>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17" t="n">
+      <c r="C16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17" t="n">
+      <c r="L16" s="1" t="n">
         <f aca="false">I16+K16/2</f>
         <v>6</v>
       </c>
-      <c r="M16" s="20" t="n">
+      <c r="M16" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C16,E16,G16,L16),0)</f>
         <v>7</v>
       </c>
-      <c r="N16" s="20" t="str">
+      <c r="N16" s="8" t="str">
         <f aca="false">IF(M16&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O16" s="17" t="n">
+      <c r="O16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17" t="n">
+      <c r="Q16" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="R16" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S16" s="20" t="n">
+      <c r="R16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O16:R16,M16),0)</f>
         <v>8</v>
       </c>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V16" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA16" s="18" t="s">
+      <c r="U16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA16" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AB16" s="18" t="n">
+      <c r="AB16" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AC16" s="18" t="n">
+      <c r="AC16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="17" t="n">
+      <c r="AD16" s="1" t="n">
         <f aca="false">AB16+AC16/2</f>
         <v>10.5</v>
       </c>
-      <c r="AE16" s="20" t="n">
+      <c r="AE16" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z16,X16,V16,AD16),0)</f>
         <v>9</v>
       </c>
-      <c r="AF16" s="20" t="n">
+      <c r="AF16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S16,AE16),0)</f>
         <v>9</v>
       </c>
-      <c r="AG16" s="20"/>
-      <c r="AH16" s="20"/>
-      <c r="AJ16" s="17"/>
-    </row>
-    <row r="17" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="18" t="s">
+    </row>
+    <row r="17" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17" t="n">
+      <c r="C17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="1" t="n">
         <f aca="false">I17+K17/2</f>
         <v>8.5</v>
       </c>
-      <c r="M17" s="20" t="n">
+      <c r="M17" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,L17),0)</f>
         <v>9</v>
       </c>
-      <c r="N17" s="20" t="str">
+      <c r="N17" s="8" t="str">
         <f aca="false">IF(M17&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O17" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="R17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S17" s="20" t="n">
+      <c r="O17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S17" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O17:R17,M17),0)</f>
         <v>9</v>
       </c>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V17" s="17" t="n">
+      <c r="U17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17" t="n">
+      <c r="X17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA17" s="18" t="s">
+      <c r="Z17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AB17" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC17" s="18" t="n">
+      <c r="AB17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD17" s="17" t="n">
+      <c r="AD17" s="1" t="n">
         <f aca="false">AB17+AC17/2</f>
         <v>11.5</v>
       </c>
-      <c r="AE17" s="20" t="n">
+      <c r="AE17" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z17,X17,V17,AD17),0)</f>
         <v>9</v>
       </c>
-      <c r="AF17" s="20" t="n">
+      <c r="AF17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S17,AE17),0)</f>
         <v>9</v>
       </c>
-      <c r="AG17" s="20"/>
-      <c r="AH17" s="20"/>
-      <c r="AJ17" s="17"/>
-    </row>
-    <row r="18" s="18" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="n">
+    </row>
+    <row r="18" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17" t="n">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17" t="n">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17" t="n">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17" t="n">
+      <c r="J18" s="1"/>
+      <c r="K18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="1" t="n">
         <f aca="false">I18+K18/2</f>
         <v>1</v>
       </c>
-      <c r="M18" s="20" t="n">
+      <c r="M18" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C18,E18,G18,L18),0)</f>
         <v>2</v>
       </c>
-      <c r="N18" s="20" t="str">
+      <c r="N18" s="8" t="str">
         <f aca="false">IF(M18&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O18" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17" t="n">
+      <c r="O18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1" t="n">
         <v>7.5</v>
       </c>
-      <c r="R18" s="17" t="n">
+      <c r="R18" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S18" s="20" t="n">
+      <c r="S18" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O18:R18,M18),0)</f>
         <v>7</v>
       </c>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V18" s="17" t="n">
+      <c r="T18" s="1"/>
+      <c r="U18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V18" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="17" t="n">
+      <c r="W18" s="1"/>
+      <c r="X18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC18" s="17" t="n">
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" s="17" t="n">
+      <c r="AD18" s="1" t="n">
         <f aca="false">AB18+AC18/2</f>
         <v>8</v>
       </c>
-      <c r="AE18" s="20" t="n">
+      <c r="AE18" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z18,X18,V18,AD18),0)</f>
         <v>7</v>
       </c>
-      <c r="AF18" s="20" t="n">
+      <c r="AF18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S18,AE18),0)</f>
         <v>7</v>
       </c>
-      <c r="AG18" s="20"/>
-      <c r="AH18" s="20"/>
-      <c r="AI18" s="17" t="n">
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AJ18" s="17"/>
-      <c r="AK18" s="17" t="n">
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AL18" s="17" t="n">
+      <c r="AL18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN18" s="18" t="n">
+      <c r="AN18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AO18" s="18" t="s">
+      <c r="AO18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="XFC18" s="21"/>
-      <c r="XFD18" s="21"/>
-    </row>
-    <row r="19" s="18" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="n">
+      <c r="XFC18" s="1"/>
+      <c r="XFD18" s="1"/>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17" t="n">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="I19" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="19" t="n">
+      <c r="I19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="K19" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="1" t="n">
         <f aca="false">I19+K19/2</f>
         <v>9.5</v>
       </c>
-      <c r="M19" s="20" t="n">
+      <c r="M19" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C19,E19,G19,L19),0)</f>
         <v>6</v>
       </c>
-      <c r="N19" s="20" t="str">
+      <c r="N19" s="8" t="str">
         <f aca="false">IF(M19&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O19" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17" t="n">
+      <c r="O19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="R19" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S19" s="20" t="n">
+      <c r="R19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O19:R19,M19),0)</f>
         <v>7</v>
       </c>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17" t="s">
+      <c r="T19" s="1"/>
+      <c r="U19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="V19" s="17" t="n">
+      <c r="V19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y19" s="19" t="n">
+      <c r="W19" s="1"/>
+      <c r="X19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y19" s="3" t="n">
         <v>45994</v>
       </c>
-      <c r="Z19" s="17" t="n">
+      <c r="Z19" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC19" s="17" t="n">
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" s="17" t="n">
+      <c r="AD19" s="1" t="n">
         <f aca="false">AB19+AC19/2</f>
         <v>8</v>
       </c>
-      <c r="AE19" s="20" t="n">
+      <c r="AE19" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z19,X19,VA2:XFD24),0)</f>
         <v>8</v>
       </c>
-      <c r="AF19" s="20" t="n">
+      <c r="AF19" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S19,AE19),0)</f>
         <v>8</v>
       </c>
-      <c r="AG19" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH19" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ19" s="17"/>
-      <c r="AL19" s="17" t="n">
+      <c r="AG19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ19" s="1"/>
+      <c r="AL19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AM19" s="18" t="n">
+      <c r="AM19" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(X19,Z19,AG19,AH19),0)</f>
         <v>8</v>
       </c>
-      <c r="AN19" s="18" t="n">
+      <c r="AN19" s="2" t="n">
         <f aca="false">ROUND(AM19*6/10,0)</f>
         <v>5</v>
       </c>
-      <c r="AO19" s="18" t="s">
+      <c r="AO19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="XFC19" s="0"/>
-      <c r="XFD19" s="0"/>
-    </row>
-    <row r="20" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="n">
+      <c r="XFC19" s="1"/>
+      <c r="XFD19" s="1"/>
+    </row>
+    <row r="20" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17" t="n">
+      <c r="C20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H20" s="3" t="n">
         <v>45881</v>
       </c>
-      <c r="I20" s="17" t="n">
+      <c r="I20" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="19" t="n">
+      <c r="J20" s="3" t="n">
         <v>45881</v>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="K20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="17" t="n">
+      <c r="L20" s="1" t="n">
         <f aca="false">I20+K20/2</f>
         <v>7</v>
       </c>
-      <c r="M20" s="20" t="n">
+      <c r="M20" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C20,E20,G20,L20),0)</f>
         <v>6</v>
       </c>
-      <c r="N20" s="20" t="str">
+      <c r="N20" s="8" t="str">
         <f aca="false">IF(M20&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O20" s="17" t="n">
+      <c r="O20" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="17" t="n">
+      <c r="P20" s="3"/>
+      <c r="Q20" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="R20" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S20" s="20" t="n">
+      <c r="R20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(M20,O20,Q20,R20),0)</f>
         <v>7</v>
       </c>
-      <c r="T20" s="17" t="s">
+      <c r="T20" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="U20" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V20" s="17" t="n">
+      <c r="U20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V20" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W20" s="17"/>
-      <c r="X20" s="17" t="n">
+      <c r="X20" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="17" t="n">
+      <c r="Z20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AA20" s="17"/>
-      <c r="AB20" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC20" s="17" t="n">
+      <c r="AB20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="17" t="n">
+      <c r="AD20" s="1" t="n">
         <f aca="false">AB20+AC20/2</f>
         <v>10</v>
       </c>
-      <c r="AE20" s="20" t="n">
+      <c r="AE20" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z20,X20,V20,AD20),0)</f>
         <v>6</v>
       </c>
-      <c r="AF20" s="20" t="n">
+      <c r="AF20" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AG20" s="20"/>
-      <c r="AH20" s="20"/>
-      <c r="AI20" s="17" t="n">
+      <c r="AI20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AJ20" s="17"/>
-      <c r="AK20" s="17" t="n">
+      <c r="AK20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AL20" s="17" t="n">
+      <c r="AL20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AN20" s="21" t="n">
+      <c r="AN20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AO20" s="21" t="s">
+      <c r="AO20" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="XFC20" s="0"/>
-      <c r="XFD20" s="0"/>
-    </row>
-    <row r="21" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="n">
+    </row>
+    <row r="21" s="9" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17" t="n">
+      <c r="C21" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="19" t="n">
+      <c r="H21" s="4" t="n">
         <v>45784</v>
       </c>
-      <c r="I21" s="17" t="n">
+      <c r="I21" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="4" t="n">
         <v>45784</v>
       </c>
-      <c r="K21" s="17" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="9" t="n">
         <f aca="false">I21+K21/2</f>
         <v>4</v>
       </c>
-      <c r="M21" s="20" t="n">
+      <c r="M21" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(C21,E21,G21,L21),0)</f>
-        <v>6</v>
-      </c>
-      <c r="N21" s="20" t="str">
+        <v>7</v>
+      </c>
+      <c r="N21" s="9" t="str">
         <f aca="false">IF(M21&lt;7,"TEP","TEA")</f>
-        <v>TEP</v>
-      </c>
-      <c r="O21" s="17" t="n">
+        <v>TEA</v>
+      </c>
+      <c r="O21" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17" t="n">
+      <c r="Q21" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="R21" s="17" t="n">
+      <c r="R21" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="S21" s="20" t="n">
+      <c r="S21" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(O21:R21,M21),0)</f>
         <v>6</v>
       </c>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17" t="s">
+      <c r="U21" s="9" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" s="17"/>
+        <v>8</v>
+      </c>
       <c r="X21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA21" s="17"/>
-      <c r="AB21" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" s="17" t="n">
+      <c r="AC21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" s="17" t="n">
+      <c r="AD21" s="9" t="n">
         <f aca="false">AB21+AC21/2</f>
         <v>0</v>
       </c>
-      <c r="AE21" s="20" t="n">
+      <c r="AE21" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(Z21,X21,V21,AD21),0)</f>
-        <v>1</v>
-      </c>
-      <c r="AF21" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(S21,AE21),0)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AG21" s="20"/>
-      <c r="AH21" s="20"/>
-      <c r="AJ21" s="17"/>
-      <c r="XFC21" s="0"/>
-      <c r="XFD21" s="0"/>
-    </row>
-    <row r="22" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="17" t="n">
+      <c r="F22" s="3" t="n">
+        <v>45783</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>45784</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="19" t="n">
+      <c r="J22" s="3" t="n">
         <v>45783</v>
       </c>
-      <c r="G22" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>45784</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="19" t="n">
-        <v>45783</v>
-      </c>
-      <c r="K22" s="17" t="n">
+      <c r="K22" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L22" s="17" t="n">
+      <c r="L22" s="1" t="n">
         <f aca="false">I22+K22/2</f>
         <v>12</v>
       </c>
-      <c r="M22" s="20" t="n">
+      <c r="M22" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C22,E22,G22,L22),0)</f>
         <v>8</v>
       </c>
-      <c r="N22" s="20" t="str">
+      <c r="N22" s="8" t="str">
         <f aca="false">IF(M22&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O22" s="17" t="n">
+      <c r="O22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17" t="n">
+      <c r="Q22" s="1" t="n">
         <v>7.5</v>
       </c>
-      <c r="R22" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S22" s="20" t="n">
+      <c r="R22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S22" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O22:R22,M22),0)</f>
         <v>7</v>
       </c>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17" t="s">
+      <c r="U22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="V22" s="17" t="n">
+      <c r="V22" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17" t="n">
+      <c r="X22" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Y22" s="17" t="s">
+      <c r="Y22" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Z22" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="18" t="s">
+      <c r="Z22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AB22" s="18" t="n">
+      <c r="AB22" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AC22" s="18" t="n">
+      <c r="AC22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AD22" s="17" t="n">
+      <c r="AD22" s="1" t="n">
         <f aca="false">AB22+AC22/2</f>
         <v>10.5</v>
       </c>
-      <c r="AE22" s="20" t="n">
+      <c r="AE22" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z22,X22,V22,AD22),0)</f>
         <v>8</v>
       </c>
-      <c r="AF22" s="20" t="n">
+      <c r="AF22" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S22,AE22),0)</f>
         <v>8</v>
       </c>
-      <c r="AG22" s="20"/>
-      <c r="AH22" s="20"/>
-      <c r="AJ22" s="17"/>
-      <c r="XFC22" s="0"/>
-      <c r="XFD22" s="0"/>
-    </row>
-    <row r="23" s="21" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="n">
+    </row>
+    <row r="23" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="19" t="n">
+      <c r="C23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3" t="n">
         <v>45767</v>
       </c>
-      <c r="E23" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17" t="n">
+      <c r="E23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H23" s="19" t="n">
+      <c r="H23" s="3" t="n">
         <v>45782</v>
       </c>
-      <c r="I23" s="17" t="n">
+      <c r="I23" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J23" s="19" t="n">
+      <c r="J23" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="K23" s="17" t="n">
+      <c r="K23" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="1" t="n">
         <f aca="false">I23+K23/2</f>
         <v>10</v>
       </c>
-      <c r="M23" s="20" t="n">
+      <c r="M23" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C23,E23,G23,L23),0)</f>
         <v>8</v>
       </c>
-      <c r="N23" s="20" t="str">
+      <c r="N23" s="8" t="str">
         <f aca="false">IF(M23&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
-      <c r="O23" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="R23" s="17" t="n">
+      <c r="O23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="S23" s="20" t="n">
+      <c r="S23" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O23:R23,M23),0)</f>
         <v>9</v>
       </c>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V23" s="17" t="n">
+      <c r="U23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V23" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC23" s="17" t="n">
+      <c r="X23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC23" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AD23" s="17" t="n">
+      <c r="AD23" s="1" t="n">
         <f aca="false">AB23+AC23/2</f>
         <v>13.5</v>
       </c>
-      <c r="AE23" s="20" t="n">
+      <c r="AE23" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z23,X23,V23,AD23),0)</f>
         <v>10</v>
       </c>
-      <c r="AF23" s="20" t="n">
+      <c r="AF23" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(S23,AE23),0)</f>
         <v>10</v>
       </c>
-      <c r="AG23" s="20"/>
-      <c r="AH23" s="20"/>
-      <c r="AJ23" s="17"/>
-      <c r="XFC23" s="0"/>
-      <c r="XFD23" s="0"/>
-    </row>
-    <row r="24" s="18" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="n">
+    </row>
+    <row r="24" s="2" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17" t="n">
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="19" t="n">
+      <c r="H24" s="3" t="n">
         <v>45784</v>
       </c>
-      <c r="I24" s="17" t="n">
+      <c r="I24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17" t="n">
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L24" s="17" t="n">
+      <c r="L24" s="1" t="n">
         <f aca="false">I24+K24/2</f>
         <v>2.5</v>
       </c>
-      <c r="M24" s="20" t="n">
+      <c r="M24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,G24,L24),0)</f>
         <v>4</v>
       </c>
-      <c r="N24" s="20" t="str">
+      <c r="N24" s="8" t="str">
         <f aca="false">IF(M24&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="O24" s="17" t="n">
+      <c r="O24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="R24" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="S24" s="20" t="n">
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="S24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(O24:R24,M24),0)</f>
         <v>8</v>
       </c>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V24" s="17" t="n">
+      <c r="T24" s="1"/>
+      <c r="U24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="V24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17" t="n">
+      <c r="W24" s="1"/>
+      <c r="X24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Y24" s="19" t="n">
+      <c r="Y24" s="3" t="n">
         <v>46001</v>
       </c>
-      <c r="Z24" s="17" t="n">
+      <c r="Z24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AA24" s="18" t="s">
+      <c r="AA24" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AB24" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC24" s="18" t="n">
+      <c r="AB24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="17" t="n">
+      <c r="AD24" s="1" t="n">
         <f aca="false">AB24+AC24/2</f>
         <v>8</v>
       </c>
-      <c r="AE24" s="20" t="n">
+      <c r="AE24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(Z24,X24,V24,AD24),0)</f>
         <v>7</v>
       </c>
-      <c r="AF24" s="20" t="n">
+      <c r="AF24" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA24,Y24,W24,AE24),0)</f>
         <v>23004</v>
       </c>
-      <c r="AG24" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH24" s="20" t="n">
+      <c r="AG24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH24" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AJ24" s="17"/>
-      <c r="AL24" s="17" t="n">
+      <c r="AJ24" s="1"/>
+      <c r="AL24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AM24" s="18" t="n">
+      <c r="AM24" s="2" t="n">
         <f aca="false">ROUND(AVERAGE(X24,Z24,AG24,AH24),0)</f>
         <v>7</v>
       </c>
-      <c r="AN24" s="18" t="n">
+      <c r="AN24" s="2" t="n">
         <f aca="false">ROUND(AM24*6/10,0)</f>
         <v>4</v>
       </c>
-      <c r="AO24" s="18" t="s">
+      <c r="AO24" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="XFC24" s="0"/>
-      <c r="XFD24" s="0"/>
+      <c r="XFC24" s="1"/>
+      <c r="XFD24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U25" s="1" t="n">
